--- a/sheets/민요/검수/창부타령 (멜로디버전).xlsx
+++ b/sheets/민요/검수/창부타령 (멜로디버전).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4333,12 +4333,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I120" s="2"/>
@@ -4995,7 +4995,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5023,20 +5023,20 @@
       <c r="E5" s="10"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="10"/>
@@ -5048,14 +5048,14 @@
       <c r="M5" s="10"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5427,7 +5427,7 @@
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5543,7 +5543,7 @@
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5568,7 +5568,7 @@
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5587,7 +5587,7 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5604,7 +5604,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="10"/>

--- a/sheets/민요/검수/창부타령 (멜로디버전).xlsx
+++ b/sheets/민요/검수/창부타령 (멜로디버전).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4850,821 +4891,821 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">창부타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="M3" s="22"/>
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="O3" s="22"/>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="18" t="inlineStr">
+      <c r="Q3" s="22"/>
+      <c r="R3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="18" t="inlineStr">
+      <c r="S3" s="24"/>
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U3" s="11"/>
+      <c r="U3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="Q4" s="25"/>
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="S4" s="25"/>
+      <c r="T4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U4" s="9"/>
+      <c r="U4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="26"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="26"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="26"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="26"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="Q5" s="26"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="S5" s="26"/>
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="26"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="22"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="Q6" s="22"/>
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S6" s="8"/>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="S6" s="22"/>
+      <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U6" s="8"/>
+      <c r="U6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="25"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢
 汰</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢
 汰</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="25"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢
 汰</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="Q7" s="25"/>
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S7" s="9"/>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="S7" s="25"/>
+      <c r="T7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U7" s="9"/>
+      <c r="U7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="26"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="I8" s="26"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="26"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="26"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="Q8" s="26"/>
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="S8" s="26"/>
+      <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U8" s="10"/>
+      <c r="U8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="22"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="O9" s="22"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="Q9" s="22"/>
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S9" s="8"/>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="S9" s="22"/>
+      <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U9" s="8"/>
+      <c r="U9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="27"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="K10" s="25"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="M10" s="27"/>
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="27"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="18" t="inlineStr">
+      <c r="Q10" s="25"/>
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="S10" s="27"/>
+      <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U10" s="9"/>
+      <c r="U10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="26"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="26"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="M11" s="26"/>
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="O11" s="28"/>
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="Q11" s="28"/>
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="S11" s="26"/>
+      <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="U11" s="10"/>
+      <c r="U11" s="26"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="C12" s="24"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="24"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="24"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="18" t="inlineStr">
+      <c r="Q12" s="22"/>
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="17" t="inlineStr">
+      <c r="S12" s="24"/>
+      <c r="T12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U12" s="8"/>
+      <c r="U12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="18" t="inlineStr">
+      <c r="S13" s="25"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U13" s="12"/>
+      <c r="U13" s="27"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="28"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="28"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="M14" s="28"/>
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="18" t="inlineStr">
+      <c r="O14" s="28"/>
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="18" t="inlineStr">
+      <c r="Q14" s="28"/>
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S14" s="13"/>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="S14" s="28"/>
+      <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/창부타령 (멜로디버전).xlsx
+++ b/sheets/민요/검수/창부타령 (멜로디버전).xlsx
@@ -4864,32 +4864,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5048,17 +5048,17 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="26"/>
@@ -5083,7 +5083,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="26"/>
@@ -5109,12 +5109,12 @@
       <c r="S5" s="26"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S6" s="22"/>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5242,12 +5242,12 @@
       <c r="S7" s="25"/>
       <c r="T7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5305,12 +5305,12 @@
       <c r="S8" s="26"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="U10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="U11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5574,11 +5574,11 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="25"/>
@@ -5603,7 +5603,7 @@
       <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="25"/>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="U13" s="27"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5664,13 +5664,13 @@
       <c r="G14" s="28"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="26"/>

--- a/sheets/민요/검수/창부타령 (멜로디버전).xlsx
+++ b/sheets/민요/검수/창부타령 (멜로디버전).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4923,66 +4946,66 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="29"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
+      <c r="K3" s="29"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="29"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O3" s="22"/>
+      <c r="O3" s="29"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q3" s="22"/>
+      <c r="Q3" s="29"/>
       <c r="R3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S3" s="24"/>
+      <c r="S3" s="30"/>
       <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U3" s="24"/>
+      <c r="U3" s="30"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -4991,62 +5014,62 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="31"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="31"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S4" s="25"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U4" s="25"/>
+      <c r="U4" s="31"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -5055,64 +5078,64 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="26"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O5" s="26"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q5" s="26"/>
+      <c r="Q5" s="32"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S5" s="26"/>
+      <c r="S5" s="32"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="26"/>
+      <c r="U5" s="32"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -5121,64 +5144,64 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K6" s="22"/>
+      <c r="K6" s="29"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="29"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O6" s="22"/>
+      <c r="O6" s="29"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q6" s="22"/>
+      <c r="Q6" s="29"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S6" s="22"/>
+      <c r="S6" s="29"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U6" s="22"/>
+      <c r="U6" s="29"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -5187,65 +5210,65 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢
 汰</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M7" s="25"/>
+      <c r="M7" s="31"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢
 汰</t>
         </is>
       </c>
-      <c r="O7" s="25"/>
+      <c r="O7" s="31"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢
 汰</t>
         </is>
       </c>
-      <c r="Q7" s="25"/>
+      <c r="Q7" s="31"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S7" s="25"/>
+      <c r="S7" s="31"/>
       <c r="T7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U7" s="25"/>
+      <c r="U7" s="31"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -5254,61 +5277,61 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="21"/>
-      <c r="K8" s="26"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M8" s="26"/>
+      <c r="M8" s="32"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q8" s="26"/>
+      <c r="Q8" s="32"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="S8" s="26"/>
+      <c r="S8" s="32"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="26"/>
+      <c r="U8" s="32"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -5317,63 +5340,63 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="29"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="K9" s="22"/>
+      <c r="K9" s="29"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M9" s="22"/>
+      <c r="M9" s="29"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="29"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="22"/>
+      <c r="Q9" s="29"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S9" s="22"/>
+      <c r="S9" s="29"/>
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U9" s="22"/>
+      <c r="U9" s="29"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -5383,68 +5406,68 @@
 僙</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="M10" s="27"/>
+      <c r="M10" s="33"/>
       <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O10" s="27"/>
+      <c r="O10" s="33"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="31"/>
       <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="S10" s="27"/>
+      <c r="S10" s="33"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U10" s="25"/>
+      <c r="U10" s="31"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -5453,62 +5476,62 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="26"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="K11" s="26"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="26"/>
+      <c r="M11" s="32"/>
       <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O11" s="28"/>
+      <c r="O11" s="34"/>
       <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="34"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="26"/>
+      <c r="S11" s="32"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="U11" s="26"/>
+      <c r="U11" s="32"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -5517,62 +5540,62 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M12" s="24"/>
+      <c r="M12" s="30"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="29"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q12" s="22"/>
+      <c r="Q12" s="29"/>
       <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S12" s="24"/>
+      <c r="S12" s="30"/>
       <c r="T12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="U12" s="22"/>
+      <c r="U12" s="29"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -5581,65 +5604,65 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O13" s="25"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="U13" s="27"/>
+      <c r="U13" s="33"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -5648,64 +5671,64 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M14" s="28"/>
+      <c r="M14" s="34"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="O14" s="28"/>
+      <c r="O14" s="34"/>
       <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="Q14" s="28"/>
+      <c r="Q14" s="34"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="S14" s="28"/>
+      <c r="S14" s="34"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U14" s="26"/>
+      <c r="U14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/창부타령 (멜로디버전).xlsx
+++ b/sheets/민요/검수/창부타령 (멜로디버전).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,22 +236,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -365,7 +348,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -377,7 +360,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
@@ -401,7 +384,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 17%</t>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
         </is>
       </c>
     </row>
@@ -429,7 +412,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12. 제목 "창부타령 '멜로디버전'". 가사 칸 없는 멜로디(율명)만 적은 양식이라 가사는 모두 비움. 오른쪽부터 1줄, 10줄 사용. 亻黃(배황종)은 僙으로 적음. 가운데 일부 칸은 원본에 잉크 번짐이 있음. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12, 10줄. 각 율명 열 오른쪽 가사 칸은 모두 비어 있음(멜로디만). 짝수 줄(2·4·8·10)은 거의 같은 南/無南/無潢/仲姑 가락 반복, 3·7줄 동일. 5·6줄 가운데 잉크 번짐. 이전 판독의 姑/僙 대부분은 南/姑의 오독이라 정정.</t>
         </is>
       </c>
     </row>
@@ -615,23 +598,19 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|仲</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲</t>
+        </is>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -657,12 +636,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -727,12 +706,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -832,12 +811,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -867,12 +846,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -902,12 +882,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -937,12 +918,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -970,23 +952,19 @@
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+姑</t>
+        </is>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13">
@@ -1045,22 +1023,18 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
     <row r="15">
@@ -1122,12 +1096,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1192,12 +1166,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I18" s="2"/>
@@ -1227,12 +1202,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I19" s="2"/>
@@ -1262,12 +1238,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I20" s="2"/>
@@ -1295,23 +1272,19 @@
       <c r="F21" s="2">
         <v>3</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+姑</t>
+        </is>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
     <row r="22">
@@ -1370,22 +1343,18 @@
       <c r="F23" s="2">
         <v>4</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1445,22 +1414,18 @@
       <c r="F25" s="2">
         <v>4</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1486,12 +1451,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I26" s="2"/>
@@ -1592,13 +1558,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -1628,13 +1593,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢|汰</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢
-汰</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I30" s="2"/>
@@ -1664,13 +1629,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1733,50 +1698,55 @@
       <c r="F33" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">번짐 심함. 아래 글자 南으로 봄(7줄 같은 가락)</t>
+        </is>
+      </c>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령.png</t>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>3</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無|潢</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
-        </is>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령.png</t>
-        </is>
-      </c>
-      <c r="C34" s="2">
-        <v>3</v>
-      </c>
-      <c r="D34" s="2">
-        <v>3</v>
-      </c>
-      <c r="E34" s="2">
-        <v>9</v>
-      </c>
-      <c r="F34" s="2">
-        <v>3</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
         </is>
       </c>
       <c r="I34" s="3"/>
@@ -1845,12 +1815,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1878,23 +1849,19 @@
       <c r="F37" s="2">
         <v>4</v>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I37" s="3"/>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+姑</t>
+        </is>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -1920,13 +1887,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I38" s="2"/>
@@ -1956,12 +1922,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I39" s="2"/>
@@ -1991,13 +1957,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-無</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I40" s="2"/>
@@ -2027,13 +1992,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2063,13 +2027,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢|汰</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢
-汰</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I42" s="2"/>
@@ -2099,12 +2063,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
@@ -2135,12 +2099,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I44" s="2"/>
@@ -2168,23 +2133,19 @@
       <c r="F45" s="2">
         <v>3</v>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|潢</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번짐 있음</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
     <row r="46">
@@ -2208,22 +2169,18 @@
       <c r="F46" s="2">
         <v>3</v>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번짐 있음</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
     <row r="47">
@@ -2249,12 +2206,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I47" s="2"/>
@@ -2284,12 +2241,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">–
+仲</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2317,23 +2275,18 @@
       <c r="F49" s="2">
         <v>4</v>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50">
@@ -2359,12 +2312,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I50" s="2"/>
@@ -2394,12 +2348,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I51" s="2"/>
@@ -2429,12 +2383,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I52" s="2"/>
@@ -2464,12 +2418,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I53" s="2"/>
@@ -2499,12 +2453,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2527,19 +2481,20 @@
         <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">㳞|湳</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">㳞
+湳</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2562,19 +2517,20 @@
         <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" s="2">
         <v>3</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I56" s="2"/>
@@ -2597,26 +2553,25 @@
         <v>5</v>
       </c>
       <c r="E57" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" s="2">
         <v>3</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|僙</t>
+          <t xml:space="preserve">潢無</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-僙</t>
+          <t xml:space="preserve">潢無</t>
         </is>
       </c>
       <c r="I57" s="3"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
+          <t xml:space="preserve">潢 오른쪽 아래에 無 작게 나란히</t>
         </is>
       </c>
       <c r="K57" s="2"/>
@@ -2637,19 +2592,19 @@
         <v>5</v>
       </c>
       <c r="E58" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -2672,27 +2627,23 @@
         <v>5</v>
       </c>
       <c r="E59" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
       </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I59" s="3"/>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="4"/>
       <c r="K59" s="2"/>
     </row>
     <row r="60">
@@ -2711,20 +2662,19 @@
         <v>5</v>
       </c>
       <c r="E60" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="2">
         <v>4</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -2741,31 +2691,32 @@
         </is>
       </c>
       <c r="C61" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
+          <t xml:space="preserve">아래 글자 흘림 氵姑(㴌)로 봄</t>
         </is>
       </c>
       <c r="K61" s="2"/>
@@ -2786,20 +2737,19 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I62" s="2"/>
@@ -2822,19 +2772,19 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="2">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I63" s="2"/>
@@ -2857,19 +2807,19 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -2892,19 +2842,20 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" s="2">
         <v>2</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -2927,19 +2878,20 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F66" s="2">
         <v>2</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -2967,19 +2919,23 @@
       <c r="F67" s="2">
         <v>3</v>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|汰</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|㴌</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="4"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">번짐 있음</t>
+        </is>
+      </c>
       <c r="K67" s="2"/>
     </row>
     <row r="68">
@@ -3005,13 +2961,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3041,12 +2996,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">–
+無</t>
         </is>
       </c>
       <c r="I69" s="2"/>
@@ -3076,13 +3032,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I70" s="2"/>
@@ -3112,12 +3067,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I71" s="2"/>
@@ -3182,12 +3137,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
@@ -3253,12 +3208,13 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+無</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3288,12 +3244,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I76" s="2"/>
@@ -3323,13 +3279,13 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㴌|湳</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">㴌
+湳</t>
         </is>
       </c>
       <c r="I77" s="2"/>
@@ -3359,13 +3315,13 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -3395,13 +3351,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I79" s="2"/>
@@ -3431,12 +3386,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I80" s="2"/>
@@ -3466,13 +3422,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-無</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -3502,12 +3458,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I82" s="2"/>
@@ -3537,12 +3493,13 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I83" s="2"/>
@@ -3572,12 +3529,13 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3607,13 +3565,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I85" s="2"/>
@@ -3643,12 +3600,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I86" s="2"/>
@@ -3678,13 +3635,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-無</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I87" s="2"/>
@@ -3714,13 +3670,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I88" s="2"/>
@@ -3750,13 +3705,13 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢|汰</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢
-汰</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I89" s="2"/>
@@ -3786,12 +3741,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
@@ -3822,12 +3777,13 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I91" s="2"/>
@@ -3857,13 +3813,13 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-潢</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I92" s="2"/>
@@ -3893,12 +3849,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I93" s="2"/>
@@ -3928,12 +3884,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I94" s="2"/>
@@ -3963,12 +3919,13 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">–
+仲</t>
         </is>
       </c>
       <c r="I95" s="2"/>
@@ -3996,23 +3953,18 @@
       <c r="F96" s="2">
         <v>4</v>
       </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I96" s="3"/>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I96" s="2"/>
+      <c r="J96" s="4"/>
       <c r="K96" s="2"/>
     </row>
     <row r="97">
@@ -4038,12 +3990,13 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I97" s="2"/>
@@ -4073,12 +4026,12 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I98" s="2"/>
@@ -4108,12 +4061,12 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I99" s="2"/>
@@ -4143,12 +4096,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I100" s="2"/>
@@ -4178,12 +4131,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I101" s="2"/>
@@ -4213,12 +4166,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I102" s="2"/>
@@ -4248,12 +4201,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I103" s="2"/>
@@ -4281,23 +4234,19 @@
       <c r="F104" s="2">
         <v>3</v>
       </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I104" s="3"/>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I104" s="2"/>
+      <c r="J104" s="4"/>
       <c r="K104" s="2"/>
     </row>
     <row r="105">
@@ -4323,12 +4272,13 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I105" s="2"/>
@@ -4356,22 +4306,18 @@
       <c r="F106" s="2">
         <v>4</v>
       </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I106" s="3"/>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I106" s="2"/>
+      <c r="J106" s="4"/>
       <c r="K106" s="2"/>
     </row>
     <row r="107">
@@ -4397,13 +4343,13 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|仲</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I107" s="2"/>
@@ -4431,22 +4377,19 @@
       <c r="F108" s="2">
         <v>4</v>
       </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I108" s="3"/>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I108" s="2"/>
+      <c r="J108" s="4"/>
       <c r="K108" s="2"/>
     </row>
     <row r="109">
@@ -4472,12 +4415,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I109" s="2"/>
@@ -4507,12 +4450,12 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I110" s="2"/>
@@ -4577,12 +4520,12 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I112" s="2"/>
@@ -4612,12 +4555,13 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I113" s="2"/>
@@ -4647,12 +4591,13 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無|潢</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無
+潢</t>
         </is>
       </c>
       <c r="I114" s="2"/>
@@ -4682,12 +4627,13 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無|南</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無
+南</t>
         </is>
       </c>
       <c r="I115" s="2"/>
@@ -4715,23 +4661,19 @@
       <c r="F116" s="2">
         <v>3</v>
       </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I116" s="3"/>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 亻黃(僙)로 봄</t>
-        </is>
-      </c>
+姑</t>
+        </is>
+      </c>
+      <c r="I116" s="2"/>
+      <c r="J116" s="4"/>
       <c r="K116" s="2"/>
     </row>
     <row r="117">
@@ -4790,22 +4732,18 @@
       <c r="F118" s="2">
         <v>4</v>
       </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I118" s="3"/>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(僙)로 봄</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I118" s="2"/>
+      <c r="J118" s="4"/>
       <c r="K118" s="2"/>
     </row>
     <row r="119">
@@ -4864,19 +4802,28 @@
       <c r="F120" s="2">
         <v>4</v>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I120" s="2"/>
-      <c r="J120" s="4"/>
-      <c r="K120" s="2"/>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|?</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+?</t>
+        </is>
+      </c>
+      <c r="I120" s="5"/>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">? = 끝의 갈고리(ↄ) 모양 마침 표시</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K120"/>
@@ -4912,7 +4859,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="55.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4939,796 +4886,812 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="55.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="I3" s="22"/>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="K3" s="24"/>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O3" s="22"/>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="M3" s="29"/>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O3" s="29"/>
-      <c r="P3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="S3" s="30"/>
-      <c r="T3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="U3" s="30"/>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
+      <c r="S3" s="22"/>
+      <c r="T3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲</t>
+        </is>
+      </c>
+      <c r="U3" s="22"/>
+    </row>
+    <row r="4" ht="55.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="31"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="31"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="31"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M4" s="31"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O4" s="31"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="31"/>
+      <c r="Q4" s="25"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S4" s="31"/>
+      <c r="S4" s="25"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U4" s="31"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U4" s="25"/>
+    </row>
+    <row r="5" ht="55.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="32"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="32"/>
+      <c r="E5" s="26"/>
       <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G5" s="26"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="I5" s="26"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="32"/>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="O5" s="26"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O5" s="32"/>
-      <c r="P5" s="21" t="inlineStr">
+      <c r="Q5" s="26"/>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S5" s="26"/>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U5" s="26"/>
+    </row>
+    <row r="6" ht="55.96" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O6" s="22"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S6" s="22"/>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U6" s="22"/>
+    </row>
+    <row r="7" ht="55.96" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="O7" s="25"/>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="S7" s="25"/>
+      <c r="T7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U7" s="25"/>
+    </row>
+    <row r="8" ht="55.96" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="26"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="O8" s="26"/>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="S8" s="26"/>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U8" s="26"/>
+    </row>
+    <row r="9" ht="55.96" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="K9" s="24"/>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="O9" s="22"/>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="S9" s="22"/>
+      <c r="T9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U9" s="22"/>
+    </row>
+    <row r="10" ht="55.96" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="O10" s="25"/>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="S10" s="25"/>
+      <c r="T10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="U10" s="25"/>
+    </row>
+    <row r="11" ht="55.96" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S5" s="32"/>
-      <c r="T5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U5" s="32"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M6" s="29"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O6" s="29"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S6" s="29"/>
-      <c r="T6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U6" s="29"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞潢
-汰</t>
-        </is>
-      </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="M7" s="31"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞潢
-汰</t>
-        </is>
-      </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞潢
-汰</t>
-        </is>
-      </c>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="S7" s="31"/>
-      <c r="T7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U7" s="31"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I8" s="32"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="M8" s="32"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="O8" s="32"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="S8" s="32"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U8" s="32"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="I9" s="29"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="29"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="S9" s="29"/>
-      <c r="T9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="29"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="K11" s="26"/>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢無</t>
+        </is>
+      </c>
+      <c r="M11" s="28"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O11" s="26"/>
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="M10" s="33"/>
-      <c r="N10" s="23" t="inlineStr">
+      <c r="Q11" s="28"/>
+      <c r="R11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S11" s="26"/>
+      <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O10" s="33"/>
-      <c r="P10" s="21" t="inlineStr">
+      <c r="U11" s="26"/>
+    </row>
+    <row r="12" ht="55.96" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S12" s="22"/>
+      <c r="T12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="S10" s="33"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="U10" s="31"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M11" s="32"/>
-      <c r="N11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="O11" s="34"/>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S11" s="32"/>
-      <c r="T11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="U11" s="32"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="K12" s="29"/>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="M12" s="30"/>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="S12" s="30"/>
-      <c r="T12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="U12" s="29"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+南</t>
+        </is>
+      </c>
+      <c r="U12" s="22"/>
+    </row>
+    <row r="13" ht="55.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="31"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I13" s="31"/>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="O13" s="31"/>
+      <c r="O13" s="25"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="Q13" s="31"/>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="Q13" s="25"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="23" t="inlineStr">
+      <c r="S13" s="25"/>
+      <c r="T13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="U13" s="33"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+姑</t>
+        </is>
+      </c>
+      <c r="U13" s="25"/>
+    </row>
+    <row r="14" ht="55.96" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+?</t>
+        </is>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O14" s="26"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="M14" s="34"/>
-      <c r="N14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="O14" s="34"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="S14" s="34"/>
+姑</t>
+        </is>
+      </c>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S14" s="26"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U14" s="32"/>
+      <c r="U14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
